--- a/backend/wp_templates/D/D2-1至D2-4  应收账款- 审定表明细表（Leap-常规程序）.xlsx
+++ b/backend/wp_templates/D/D2-1至D2-4  应收账款- 审定表明细表（Leap-常规程序）.xlsx
@@ -24594,7 +24594,7 @@
         <v>441</v>
       </c>
       <c r="B17" s="24">
-        <f t="shared" ref="B17:J17" si="4">SUM(B18:B20)</f>
+        <f t="shared" ref="B17:J17" si="4">SUM(B18:B21)</f>
         <v>0</v>
       </c>
       <c r="C17" s="24">
@@ -24634,11 +24634,11 @@
         <v>0</v>
       </c>
       <c r="L17" s="24">
-        <f>SUM(L18:L20)</f>
+        <f>SUM(L18:L21)</f>
         <v>0</v>
       </c>
       <c r="M17" s="24">
-        <f>SUM(M18:M20)</f>
+        <f>SUM(M18:M21)</f>
         <v>0</v>
       </c>
       <c r="N17" s="24">
@@ -24669,7 +24669,7 @@
       <c r="L18" s="26"/>
       <c r="M18" s="26"/>
       <c r="N18" s="27">
-        <f>K18+L18</f>
+        <f>K18+L18+M18</f>
         <v>0</v>
       </c>
     </row>
@@ -24694,7 +24694,7 @@
       <c r="L19" s="26"/>
       <c r="M19" s="26"/>
       <c r="N19" s="27">
-        <f>K19+L19</f>
+        <f>K19+L19+M19</f>
         <v>0</v>
       </c>
     </row>
@@ -24719,7 +24719,7 @@
       <c r="L20" s="26"/>
       <c r="M20" s="26"/>
       <c r="N20" s="27">
-        <f>K20+L20</f>
+        <f>K20+L20+M20</f>
         <v>0</v>
       </c>
     </row>
@@ -24744,7 +24744,7 @@
       <c r="L21" s="36"/>
       <c r="M21" s="36"/>
       <c r="N21" s="27">
-        <f>K21+L21</f>
+        <f>K21+L21+M21</f>
         <v>0</v>
       </c>
     </row>

--- a/backend/wp_templates/D/D2-1至D2-4  应收账款- 审定表明细表（Leap-常规程序）.xlsx
+++ b/backend/wp_templates/D/D2-1至D2-4  应收账款- 审定表明细表（Leap-常规程序）.xlsx
@@ -22931,7 +22931,10 @@
       <c r="E13" s="50"/>
       <c r="F13" s="50"/>
       <c r="G13" s="50"/>
-      <c r="H13" s="50"/>
+      <c r="H13" s="50">
+        <f>E13+F13+G13</f>
+        <v>0</v>
+      </c>
       <c r="I13" s="50"/>
       <c r="J13" s="50"/>
       <c r="K13" s="50"/>
@@ -22987,7 +22990,10 @@
       <c r="E14" s="50"/>
       <c r="F14" s="50"/>
       <c r="G14" s="50"/>
-      <c r="H14" s="50"/>
+      <c r="H14" s="50">
+        <f>E14+F14+G14</f>
+        <v>0</v>
+      </c>
       <c r="I14" s="50"/>
       <c r="J14" s="50"/>
       <c r="K14" s="50"/>
@@ -23043,7 +23049,10 @@
       <c r="E15" s="50"/>
       <c r="F15" s="50"/>
       <c r="G15" s="50"/>
-      <c r="H15" s="50"/>
+      <c r="H15" s="50">
+        <f>E15+F15+G15</f>
+        <v>0</v>
+      </c>
       <c r="I15" s="50"/>
       <c r="J15" s="50"/>
       <c r="K15" s="50"/>
@@ -23099,7 +23108,10 @@
       <c r="E16" s="50"/>
       <c r="F16" s="50"/>
       <c r="G16" s="50"/>
-      <c r="H16" s="50"/>
+      <c r="H16" s="50">
+        <f>E16+F16+G16</f>
+        <v>0</v>
+      </c>
       <c r="I16" s="50"/>
       <c r="J16" s="50"/>
       <c r="K16" s="50"/>
@@ -23155,7 +23167,10 @@
       <c r="E17" s="50"/>
       <c r="F17" s="50"/>
       <c r="G17" s="50"/>
-      <c r="H17" s="50"/>
+      <c r="H17" s="50">
+        <f>E17+F17+G17</f>
+        <v>0</v>
+      </c>
       <c r="I17" s="50"/>
       <c r="J17" s="50"/>
       <c r="K17" s="50"/>
@@ -23211,7 +23226,10 @@
       <c r="E18" s="50"/>
       <c r="F18" s="50"/>
       <c r="G18" s="50"/>
-      <c r="H18" s="50"/>
+      <c r="H18" s="50">
+        <f>E18+F18+G18</f>
+        <v>0</v>
+      </c>
       <c r="I18" s="50"/>
       <c r="J18" s="50"/>
       <c r="K18" s="50"/>
@@ -23267,7 +23285,10 @@
       <c r="E19" s="50"/>
       <c r="F19" s="50"/>
       <c r="G19" s="50"/>
-      <c r="H19" s="50"/>
+      <c r="H19" s="50">
+        <f>E19+F19+G19</f>
+        <v>0</v>
+      </c>
       <c r="I19" s="50"/>
       <c r="J19" s="50"/>
       <c r="K19" s="50"/>
@@ -23319,7 +23340,10 @@
       <c r="E20" s="50"/>
       <c r="F20" s="50"/>
       <c r="G20" s="50"/>
-      <c r="H20" s="50"/>
+      <c r="H20" s="50">
+        <f>E20+F20+G20</f>
+        <v>0</v>
+      </c>
       <c r="I20" s="50"/>
       <c r="J20" s="50"/>
       <c r="K20" s="50"/>
@@ -23371,7 +23395,10 @@
       <c r="E21" s="50"/>
       <c r="F21" s="50"/>
       <c r="G21" s="50"/>
-      <c r="H21" s="50"/>
+      <c r="H21" s="50">
+        <f>E21+F21+G21</f>
+        <v>0</v>
+      </c>
       <c r="I21" s="50"/>
       <c r="J21" s="50"/>
       <c r="K21" s="50"/>
@@ -23423,7 +23450,10 @@
       <c r="E22" s="50"/>
       <c r="F22" s="50"/>
       <c r="G22" s="50"/>
-      <c r="H22" s="50"/>
+      <c r="H22" s="50">
+        <f>E22+F22+G22</f>
+        <v>0</v>
+      </c>
       <c r="I22" s="50"/>
       <c r="J22" s="50"/>
       <c r="K22" s="50"/>
@@ -23475,7 +23505,10 @@
       <c r="E23" s="50"/>
       <c r="F23" s="50"/>
       <c r="G23" s="50"/>
-      <c r="H23" s="50"/>
+      <c r="H23" s="50">
+        <f>E23+F23+G23</f>
+        <v>0</v>
+      </c>
       <c r="I23" s="50"/>
       <c r="J23" s="50"/>
       <c r="K23" s="50"/>
@@ -23527,7 +23560,10 @@
       <c r="E24" s="50"/>
       <c r="F24" s="50"/>
       <c r="G24" s="50"/>
-      <c r="H24" s="50"/>
+      <c r="H24" s="50">
+        <f>E24+F24+G24</f>
+        <v>0</v>
+      </c>
       <c r="I24" s="50"/>
       <c r="J24" s="50"/>
       <c r="K24" s="50"/>
@@ -23579,7 +23615,10 @@
       <c r="E25" s="50"/>
       <c r="F25" s="50"/>
       <c r="G25" s="50"/>
-      <c r="H25" s="50"/>
+      <c r="H25" s="50">
+        <f>E25+F25+G25</f>
+        <v>0</v>
+      </c>
       <c r="I25" s="50"/>
       <c r="J25" s="50"/>
       <c r="K25" s="50"/>
